--- a/Extracted_data_analysis/temperate/Output-Transformed_data/geographical_distribution_summary.xlsx
+++ b/Extracted_data_analysis/temperate/Output-Transformed_data/geographical_distribution_summary.xlsx
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>341</v>
+        <v>325</v>
       </c>
     </row>
     <row r="3">
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>77</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>51</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9">
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>38</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>39</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="B29">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -870,7 +870,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -897,10 +897,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>421</v>
+        <v>517</v>
       </c>
       <c r="C2">
-        <v>78</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3">
@@ -910,10 +910,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="C3">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="C4">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -936,48 +936,9 @@
         </is>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>8</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
         <v>0</v>
       </c>
     </row>
